--- a/Park Factor Project Blues.xlsx
+++ b/Park Factor Project Blues.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R CODES!!\PARK FACTORS BLUES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{421B7B55-280A-4B67-BB51-0F719F28C509}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71FA7954-9DB0-4448-B866-246E96280CA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{36984A07-DC0C-40AC-8C85-DE13333C7410}"/>
   </bookViews>
@@ -310,27 +310,27 @@
     <t>(#) indicates true rank (accounts for ties)</t>
   </si>
   <si>
-    <t>I started by porting Alan M. Nathan's baseball trajectory calculator (baseball.physics.illinois.edu/trajectory-calculator.html) into a reproducible R script, then applied it to model the flight of every fly ball in the 2026 NECBL season.
+    <t>Zone</t>
+  </si>
+  <si>
+    <t>Balls</t>
+  </si>
+  <si>
+    <t>HR_Rate</t>
+  </si>
+  <si>
+    <t>Center</t>
+  </si>
+  <si>
+    <t>Left</t>
+  </si>
+  <si>
+    <t>Right</t>
+  </si>
+  <si>
+    <t>I first recreated Alan M. Nathan's baseball trajectory calculator (baseball.physics.illinois.edu/trajectory-calculator.html) as a reproducible R script, then used this script to model the flight of every fly ball logged by trackman in the 2026 NECBL season.
 For park dimensions, I worked from five measured points per stadium (LF, LC, CF, RC, and RF distances and wall heights). Rather than interpolating wall height with false precision between points that were never actually measured, I snapped each simulated ball to the nearest real measurement. I then simulated each historical ball's full trajectory individually per park, accounting for that park's elevation, and checked the ball's height at the moment it reached the fence to determine whether it would have cleared. These results were aggregated into overall and direction-specific (left, center, right) park factor indices.
 From there, I built a model to predict which pitcher would perform best at which park. It combined each pitcher's zone-by-zone tendencies (fly ball rate, spray direction, and exit velocity allowed) against each park's zone-specific home run rate, producing an expected home run score for every pitcher-park pairing. I ranked pitchers within each park and parks within each pitcher, filtered results to a minimum reliable sample size, and exported leaderboards that included sample-size context (fly ball count, innings pitched) alongside the rankings.</t>
-  </si>
-  <si>
-    <t>Zone</t>
-  </si>
-  <si>
-    <t>Balls</t>
-  </si>
-  <si>
-    <t>HR_Rate</t>
-  </si>
-  <si>
-    <t>Center</t>
-  </si>
-  <si>
-    <t>Left</t>
-  </si>
-  <si>
-    <t>Right</t>
   </si>
 </sst>
 </file>
@@ -840,14 +840,13 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1225,7 +1224,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E3609D8-A60D-4A82-8A9A-E52AA1AB2AA6}">
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="94.9296875" customWidth="1"/>
@@ -1249,20 +1248,14 @@
       <c r="A2" s="4"/>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A3" s="5" t="s">
+      <c r="A3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="213.75" x14ac:dyDescent="0.45">
-      <c r="A5" s="6" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A7" s="5"/>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A9" s="5"/>
+    <row r="5" spans="1:1" ht="228" x14ac:dyDescent="0.45">
+      <c r="A5" s="5" t="s">
+        <v>101</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1971,16 +1964,16 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D1" t="s">
         <v>96</v>
-      </c>
-      <c r="D1" t="s">
-        <v>97</v>
       </c>
       <c r="E1" t="s">
         <v>1</v>
       </c>
       <c r="F1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G1" t="s">
         <v>2</v>
@@ -1994,7 +1987,7 @@
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D2">
         <v>22473</v>
@@ -2017,7 +2010,7 @@
         <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D3">
         <v>22473</v>
@@ -2040,7 +2033,7 @@
         <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D4">
         <v>22473</v>
@@ -2063,7 +2056,7 @@
         <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D5">
         <v>22473</v>
@@ -2086,7 +2079,7 @@
         <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D6">
         <v>22473</v>
@@ -2109,7 +2102,7 @@
         <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D7">
         <v>22473</v>
@@ -2132,7 +2125,7 @@
         <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D8">
         <v>22473</v>
@@ -2155,7 +2148,7 @@
         <v>9</v>
       </c>
       <c r="C9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D9">
         <v>22473</v>
@@ -2178,7 +2171,7 @@
         <v>12</v>
       </c>
       <c r="C10" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D10">
         <v>22473</v>
@@ -2201,7 +2194,7 @@
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D11">
         <v>22473</v>
@@ -2224,7 +2217,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D12">
         <v>22473</v>
@@ -2247,7 +2240,7 @@
         <v>8</v>
       </c>
       <c r="C13" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D13">
         <v>22473</v>
@@ -2270,7 +2263,7 @@
         <v>11</v>
       </c>
       <c r="C14" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D14">
         <v>22473</v>
@@ -2293,7 +2286,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D15">
         <v>8281</v>
@@ -2316,7 +2309,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D16">
         <v>8281</v>
@@ -2339,7 +2332,7 @@
         <v>8</v>
       </c>
       <c r="C17" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D17">
         <v>8281</v>
@@ -2362,7 +2355,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D18">
         <v>8281</v>
@@ -2385,7 +2378,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D19">
         <v>8281</v>
@@ -2408,7 +2401,7 @@
         <v>12</v>
       </c>
       <c r="C20" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D20">
         <v>8281</v>
@@ -2431,7 +2424,7 @@
         <v>11</v>
       </c>
       <c r="C21" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D21">
         <v>8281</v>
@@ -2454,7 +2447,7 @@
         <v>13</v>
       </c>
       <c r="C22" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D22">
         <v>8281</v>
@@ -2477,7 +2470,7 @@
         <v>9</v>
       </c>
       <c r="C23" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D23">
         <v>8281</v>
@@ -2500,7 +2493,7 @@
         <v>5</v>
       </c>
       <c r="C24" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D24">
         <v>8281</v>
@@ -2523,7 +2516,7 @@
         <v>7</v>
       </c>
       <c r="C25" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D25">
         <v>8281</v>
@@ -2546,7 +2539,7 @@
         <v>14</v>
       </c>
       <c r="C26" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D26">
         <v>8281</v>
@@ -2569,7 +2562,7 @@
         <v>15</v>
       </c>
       <c r="C27" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D27">
         <v>8281</v>
@@ -2592,7 +2585,7 @@
         <v>3</v>
       </c>
       <c r="C28" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D28">
         <v>12746</v>
@@ -2615,7 +2608,7 @@
         <v>4</v>
       </c>
       <c r="C29" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D29">
         <v>12746</v>
@@ -2638,7 +2631,7 @@
         <v>7</v>
       </c>
       <c r="C30" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D30">
         <v>12746</v>
@@ -2661,7 +2654,7 @@
         <v>5</v>
       </c>
       <c r="C31" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D31">
         <v>12746</v>
@@ -2684,7 +2677,7 @@
         <v>6</v>
       </c>
       <c r="C32" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D32">
         <v>12746</v>
@@ -2707,7 +2700,7 @@
         <v>9</v>
       </c>
       <c r="C33" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D33">
         <v>12746</v>
@@ -2730,7 +2723,7 @@
         <v>8</v>
       </c>
       <c r="C34" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D34">
         <v>12746</v>
@@ -2753,7 +2746,7 @@
         <v>10</v>
       </c>
       <c r="C35" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D35">
         <v>12746</v>
@@ -2776,7 +2769,7 @@
         <v>11</v>
       </c>
       <c r="C36" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D36">
         <v>12746</v>
@@ -2799,7 +2792,7 @@
         <v>13</v>
       </c>
       <c r="C37" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D37">
         <v>12746</v>
@@ -2822,7 +2815,7 @@
         <v>12</v>
       </c>
       <c r="C38" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D38">
         <v>12746</v>
@@ -2845,7 +2838,7 @@
         <v>14</v>
       </c>
       <c r="C39" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D39">
         <v>12746</v>
@@ -2868,7 +2861,7 @@
         <v>15</v>
       </c>
       <c r="C40" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D40">
         <v>12746</v>
